--- a/excel/2026-07-31.xlsx
+++ b/excel/2026-07-31.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,232 +476,188 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责管理一个仓库的货物重量记录。表格中有货物名称、存放区域、重量（公斤）。现在需要知道“A区”所有货物的总重量。</t>
+          <t>要求：你是销售助理，有一张本周各销售员的销售额记录表，需要快速汇总指定销售员的合计销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 B8 输入公式，计算区域为“A区”的重量总和。</t>
+          <t>任务：在E2单元格输入公式，统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>零件X</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>12.5</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>零件Y</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>B区</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8.199999999999999</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>零件Z</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>15</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>零件W</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>C区</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>9.800000000000001</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>零件Q</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>20.3</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份客户订单表，包含订单号、客户名称、发货地址。现在需要根据某个订单号（例如订单号“1003”）快速查找对应的发货地址。</t>
+          <t>要求：公司有员工名单和部门对照表，你需要在工资表中根据员工姓名填充部门，但有些员工可能不在对照表中，要显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E1 输入订单号（如1003），在单元格 F1 输入公式，根据E1中的订单号查找对应的发货地址。</t>
+          <t>任务：在F2单元格输入公式，根据E2（员工姓名）在A2:B5中查找部门，如果找不到则显示“未找到”。假设E2中已输入“李强”。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>员工姓名</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>发货地址</t>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>1001</v>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>客户甲</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>上海市浦东新区</t>
+          <t>销售部</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1002</v>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>李强</t>
+        </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>客户乙</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>北京市朝阳区</t>
+          <t>技术部</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1003</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>客户丙</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>广州市天河区</t>
+          <t>行政部</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>1004</v>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>陈杰</t>
+        </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>客户丁</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>深圳市南山区</t>
+          <t>财务部</t>
         </is>
       </c>
     </row>
@@ -715,40 +671,40 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：公司人事表中有每位员工的入职日期。请计算每位员工截至今天（2025年4月1日）的工龄（整年数），并判断是否满5年（满5年显示“是”，否则显示“否”）。假设今天固定为2025年4月1日。</t>
+          <t>要求：物流公司记录了一周的订单，需要统计指定销售员且发货状态为“已发货”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式计算张三的工龄（年），在 D2 单元格输入公式判断是否满5年（返回“是”或“否”），然后向下填充到C5:D5。</t>
+          <t>任务：在H2单元格输入公式，统计“张三”且“已发货”的订单数。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>员工姓名</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>发货状态</t>
         </is>
       </c>
     </row>
@@ -760,7 +716,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2018年6月15日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -772,236 +728,246 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2020年3月1日</t>
+          <t>未发货</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2019年11月20日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2021年7月10日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流表格中有一列货物编号，编号格式为“字母+批次号”，例如“ABC2301”中的“2301”是批次号，需要提取批次号，然后根据批次号从另一个价格表中查找该批次的单价（元/件）。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 B2 单元格输入公式提取批次号（后4位），在 C2 单元格输入公式根据批次号在右侧价格表（F2:G5）中查找单价，并向下填充。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事部需要计算员工的年龄（以年为单位），同时物流部需要计算货物到今天已存放的天数。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>ABC2301</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>50</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式计算刘洋的年龄（整年），在E2单元格输入公式计算刘洋的货物到港天数（今天设为2025-04-01）。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>DEF2302</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>30</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>出生日期</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>货物到港日期</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>GHI2303</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>20</v>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1990-05-15</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>JKL2304</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>10</v>
+          <t>陈静</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1985-08-20</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>赵磊</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售明细表记录了每个产品在不同月份的销售额。你需要计算“产品A”在“1月”的总销售额，但找数据时可能因为产品名或月份写错导致无匹配，要求若查不到结果则显示“未找到”。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 B8 输入公式，计算“产品A”且“1月”的销售额总和，若结果为0（无匹配）则显示“未找到”。</t>
+          <t>要求：商品表中有产品编号对应的名称和单价，现在有一份订单需要快速填充名称和单价。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2中的产品编号（假设为“B02”）查找产品名称；在G2输入公式，使用INDEX+MATCH查找单价。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1200</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>800</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>产品A</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1500</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>600</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1028,7 +994,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1005,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C6,B2:B6,"A区")</f>
+        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1053,7 +1019,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1030,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>XLOOKUP(E1,A2:A5,C2:C5)</f>
+        <f>IFERROR(VLOOKUP(E2,A2:B5,2,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1078,7 +1044,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1088,10 +1054,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C2: =DATEDIF(B2,"2025-4-1","y")  D2: =IF(C2&gt;=5,"是","否")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>COUNTIFS(A2:A7,"张三",B2:B7,"已发货")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1104,7 +1069,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1079,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>B2: =RIGHT(A2,4)  C2: =VLOOKUP(B2,$F$2:$G$5,2,FALSE)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>DATEDIF(B2,TODAY(),"Y") 和 =TODAY()-C2</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1130,7 +1094,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1105,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"产品A",B2:B6,"1月"),"未找到")</f>
+        <f>XLOOKUP(E2,A2:A4,B2:B4) 和 =INDEX(C2:C4,MATCH(E2,A2:A4,0))</f>
         <v/>
       </c>
     </row>
@@ -1173,7 +1137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1149,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于按多个条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,...)。本题中，求和区域是C2:C6（重量），条件区域是B2:B6（区域），条件为"A区"，因此公式会筛选区域为A区的行，将对应重量加总。</t>
+          <t>SUMIF函数语法：SUMIF(条件区域, 条件, 求和区域)。本题中A2:A7是销售员列表，条件为“张三”，B2:B7是对应销售额，函数会筛选出所有“张三”的行并求和，结果为3200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1168,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是新一代查找函数，语法为XLOOKUP(查找值,查找数组,返回数组)。本题在A2:A5中查找E1的值，找到后返回C2:C5中对应行的发货地址。相比VLOOKUP，XLOOKUP不需要指定列号，且可以向左查找。</t>
+          <t>VLOOKUP(查找值,表格区域,返回列号,精确匹配)用于查找“李强”的部门。IFERROR函数捕获错误，当查找不到时返回“未找到”。本题中“李强”存在，所以返回“技术部”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1187,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,单位)。单位"y"表示整年数。这里用入职日期到指定日期2025-4-1的年数。然后IF函数判断工龄是否&gt;=5，满足返回"是"，否则返回"否"。</t>
+          <t>COUNTIFS函数语法：COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)。分别对销售员列和状态列设置条件，同时满足的行计数。结果为2（第一行和第三行）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
@@ -1242,14 +1206,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT函数从文本右侧提取指定字符数，语法RIGHT(文本,位数)，这里提取后4位。VLOOKUP用于精确查找，语法VLOOKUP(查找值,表格区域,列号,精确/近似)，本题用FALSE精确匹配批次号，返回第2列单价。</t>
+          <t>DATEDIF(起始日期,结束日期,单位)返回两个日期之间的完整年数，年龄计算用"Y"。TODAY()返回当前日期。到港天数直接用当前日期减到港日期，得到天数差。假设今天为2025-04-01，则年龄为34岁，天数为81天。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1225,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS多条件求和：求和区域C2:C6，条件区域1为A2:A6条件"产品A"，条件区域2为B2:B6条件"1月"。如果没有任何行满足条件，SUMIFS返回0。用IFERROR包裹，当SUMIFS结果为错误时（本公式中不会出错，但若条件写错单元格引用则可能），或想将0显示为“未找到”，可以改用IF判断，但这里用IFERROR演示容错。实际若要处理0，可用IF(SUMIFS=0,"未找到",SUMIFS)，但题目要求IFERROR，所以假设无匹配时SUMIFS会返回错误（实际如果条件区域有文本但无匹配则返回0，不会报错，因此此公式会返回0，不会显示“未找到”。但为了演示IFERROR，我们可将题目改为：当产品名或月份不存在时，SUMIFS返回0，而IFERROR无法捕获0。这里调整：使用VLOOKUP查找，但为符合SUMIFS+IFERROR，我们可让用户输入产品名和月份，若输入不存在则SUMIFS返回0，但IFERROR只捕获错误。因此此答案其实不会显示“未找到”。建议修改为：=IF(SUMIFS(...)=0,"未找到",SUMIFS(...))，但题重要求IFERROR，所以只能作为示例，讲解时可说明IFERROR用于捕获错误，而SUMIFS本身不会产生错误，所以更常用IF。本答案按题要求给出。</t>
+          <t>XLOOKUP(查找值,查找数组,返回数组)直接返回对应名称，比VLOOKUP更简单。INDEX+MATCH组合：MATCH找到E2在编号列中的位置（第2行），INDEX根据位置返回单价列的值。两者结果分别为“香蕉”和3.2。</t>
         </is>
       </c>
     </row>
